--- a/etf_holdings/2026-09-15_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-09-15_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,55 +501,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>2.12%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.57%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>149139</v>
+        <v>536000</v>
       </c>
       <c r="K2" t="n">
-        <v>99139</v>
+        <v>380000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50,000</t>
+          <t>-156,000</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-09-14_00405A_full_holdings.xlsx</t>
+          <t>2026-09-14_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -559,60 +559,60 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>210000</v>
+        <v>3550000</v>
       </c>
       <c r="K3" t="n">
-        <v>130000</v>
+        <v>3700000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-80,000</t>
+          <t>150,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-09-14_00407A_full_holdings.xlsx</t>
+          <t>2026-09-14_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -627,55 +627,55 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>0.81%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>80000</v>
+        <v>2000000</v>
       </c>
       <c r="K4" t="n">
-        <v>60000</v>
+        <v>1000000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>-1,000,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-09-14_00407A_full_holdings.xlsx</t>
+          <t>2026-09-14_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -685,159 +685,456 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.97%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>325000</v>
+        <v>2640000</v>
       </c>
       <c r="K5" t="n">
-        <v>225000</v>
+        <v>2770000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-100,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-09-14_00407A_full_holdings.xlsx</t>
+          <t>2026-09-14_00403A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00405A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>減碼</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>華星光</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.57%</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>1.27%</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.89%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>-0.38%</t>
+        </is>
+      </c>
       <c r="J6" t="n">
-        <v>293000</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+        <v>149139</v>
+      </c>
+      <c r="K6" t="n">
+        <v>99139</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-50,000</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-09-14_00400A_full_holdings.xlsx</t>
+          <t>2026-09-14_00405A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.88%</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.53%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>-0.35%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>210000</v>
+      </c>
+      <c r="K7" t="n">
+        <v>130000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-80,000</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2026-09-14_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3008</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1.97%</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.53%</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>-0.44%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="K8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2026-09-14_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6805</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>富世達</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.92%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>-0.97%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>325000</v>
+      </c>
+      <c r="K9" t="n">
+        <v>225000</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-100,000</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2026-09-14_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>10TX台指期貨</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.71%</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>19</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09-14_00993A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>293000</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-09-14_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>2308</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>台達電</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>台達電</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2.58%</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>3.21%</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>+0.63%</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J12" t="n">
         <v>446000</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K12" t="n">
         <v>525000</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>79,000</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>2026-09-14_00400A_full_holdings.xlsx</t>
         </is>
